--- a/data/trans_bre/P2A_senso_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Edad-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,89</t>
+          <t>-0,28; 2,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,22</t>
+          <t>-2,26; 0,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,78</t>
+          <t>0,02; 5,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,13; —</t>
+          <t>-90,79; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 102,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,0</t>
+          <t>-0,9; 1,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,49</t>
+          <t>0,31; 3,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,41</t>
+          <t>-0,39; 1,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,1</t>
+          <t>-4,2; 0,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,62; 325,16</t>
+          <t>-82,48; 373,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,97; 1501,56</t>
+          <t>9,65; 1143,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-95,08; 26,08</t>
+          <t>-92,36; 28,35</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,07</t>
+          <t>-1,15; 1,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,83</t>
+          <t>-0,85; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,77</t>
+          <t>-1,08; 0,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,09</t>
+          <t>-1,74; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,39; 443,78</t>
+          <t>-80,86; 423,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,48; 413,11</t>
+          <t>-56,82; 449,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-82,48; 304,05</t>
+          <t>-85,86; 309,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 211,83</t>
+          <t>-72,09; 210,24</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,56</t>
+          <t>-0,64; 2,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,94</t>
+          <t>-1,91; 1,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,28</t>
+          <t>-2,77; 0,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,3</t>
+          <t>-0,9; 2,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 520,15</t>
+          <t>-45,21; 462,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,86; 141,77</t>
+          <t>-60,51; 125,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 68,4</t>
+          <t>-86,88; 41,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 314,58</t>
+          <t>-34,05; 239,68</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,83</t>
+          <t>-3,46; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,91</t>
+          <t>-1,24; 2,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,62</t>
+          <t>-2,42; 0,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,67</t>
+          <t>-2,27; 1,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 54,3</t>
+          <t>-77,44; 55,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 285,86</t>
+          <t>-48,17; 271,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 62,13</t>
+          <t>-45,56; 62,06</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -0,66</t>
+          <t>-5,8; -0,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,76</t>
+          <t>-1,86; 3,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,16</t>
+          <t>-1,35; 2,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 70,62</t>
+          <t>0,45; 68,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,47; -13,65</t>
+          <t>-88,41; -0,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,11; 453,38</t>
+          <t>-57,77; 398,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,41; 726,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,07; 3821,44</t>
+          <t>11,66; 3862,41</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,88</t>
+          <t>-1,68; 4,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,44</t>
+          <t>-4,46; 1,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,3</t>
+          <t>-0,9; 4,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,08</t>
+          <t>0,79; 5,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 555,8</t>
+          <t>-44,45; 538,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-73,01; 68,62</t>
+          <t>-70,37; 85,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 832,9</t>
+          <t>-55,61; 837,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,48; 278,97</t>
+          <t>11,31; 268,45</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,71</t>
+          <t>-0,51; 0,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,13</t>
+          <t>-0,17; 1,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,57</t>
+          <t>-0,49; 0,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 23,16</t>
+          <t>0,47; 23,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 56,33</t>
+          <t>-28,66; 58,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 80,11</t>
+          <t>-8,54; 90,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 73,93</t>
+          <t>-38,88; 69,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,06; 1225,76</t>
+          <t>19,72; 1180,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3426,4%</t>
+          <t>360,18%</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,14</t>
+          <t>-0,41; 2,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,21</t>
+          <t>-2,45; 0,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,17 +675,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,14</t>
+          <t>-0,31; 5,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-90,79; —</t>
+          <t>-81,81; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-61,94%</t>
+          <t>-56,37%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,06</t>
+          <t>-0,9; 1,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,29</t>
+          <t>0,42; 3,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,37</t>
+          <t>-0,46; 1,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,17</t>
+          <t>-4,64; 0,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,48; 373,85</t>
+          <t>-83,88; 401,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 1143,97</t>
+          <t>15,03; 1122,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-92,36; 28,35</t>
+          <t>-88,46; 75,78</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,08%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,15</t>
+          <t>-0,98; 1,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,89</t>
+          <t>-0,71; 2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,73</t>
+          <t>-1,14; 0,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,04</t>
+          <t>-0,86; 1,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,86; 423,16</t>
+          <t>-75,7; 491,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,82; 449,14</t>
+          <t>-49,07; 418,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,86; 309,12</t>
+          <t>-83,4; 318,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,09; 210,24</t>
+          <t>-48,87; 320,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>-2,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,34</t>
+          <t>-0,82; 2,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,74</t>
+          <t>-1,88; 2,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,28</t>
+          <t>-2,43; 0,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,17</t>
+          <t>-1,85; 1,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 462,67</t>
+          <t>-50,91; 459,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,51; 125,77</t>
+          <t>-57,77; 153,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-86,88; 41,26</t>
+          <t>-84,59; 42,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 239,68</t>
+          <t>-51,18; 74,52</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-4,25%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,02</t>
+          <t>-3,42; 1,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,67</t>
+          <t>-1,25; 2,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,55</t>
+          <t>-2,15; 0,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,62</t>
+          <t>-1,95; 1,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-77,44; 55,29</t>
+          <t>-76,82; 70,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,17; 271,09</t>
+          <t>-50,29; 253,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 62,06</t>
+          <t>-40,23; 73,83</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33,36</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1019,32%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -0,55</t>
+          <t>-5,91; -0,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,57</t>
+          <t>-1,56; 4,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,13</t>
+          <t>-1,35; 2,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 68,59</t>
+          <t>-0,73; 3,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,41; -0,33</t>
+          <t>-88,69; -7,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 398,7</t>
+          <t>-57,79; 469,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-83,41; 726,0</t>
+          <t>-81,9; 904,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,66; 3862,41</t>
+          <t>-18,26; 157,12</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>109,89%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 4,86</t>
+          <t>-1,44; 5,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,68</t>
+          <t>-4,22; 1,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,06</t>
+          <t>-0,76; 4,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,91</t>
+          <t>0,8; 6,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,45; 538,12</t>
+          <t>-45,89; 545,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 85,9</t>
+          <t>-69,9; 93,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 837,6</t>
+          <t>-46,67; 838,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,31; 268,45</t>
+          <t>11,97; 276,98</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>273,33%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,74</t>
+          <t>-0,48; 0,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,2</t>
+          <t>-0,2; 1,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,54</t>
+          <t>-0,43; 0,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 23,23</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 58,47</t>
+          <t>-26,27; 57,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 90,33</t>
+          <t>-11,01; 86,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 69,91</t>
+          <t>-34,58; 78,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,72; 1180,41</t>
+          <t>-0,19; 70,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
